--- a/AAII_Financials/Yearly/ZLIOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZLIOY_YR_FIN.xlsx
@@ -2206,10 +2206,10 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1506500</v>
+        <v>1488500</v>
       </c>
       <c r="E59" s="3">
-        <v>1111200</v>
+        <v>1092300</v>
       </c>
       <c r="F59" s="3">
         <v>1285400</v>
